--- a/outputs/472-15.xlsx
+++ b/outputs/472-15.xlsx
@@ -140,12 +140,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -342,107 +346,108 @@
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
+        <f aca="false">IF(ISNUMBER(SEARCH("4Ozark",A1)),1,IF(ISNUMBER(SEARCH("3Tall",A1)),2,IF(ISNUMBER(SEARCH("1Jasper",A1)),3,IF(ISNUMBER(SEARCH("2GWood",A1)),4,IF(ISNUMBER(SEARCH("5Dawson",A1)),5,IF(ISNUMBER(SEARCH("8CPark",A1)),6,""))))))</f>
         <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>1164</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <v>2421.78</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>291</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="1" t="n">
         <v>76.29</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>833</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="1" t="n">
         <v>1252.88</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="1" t="n">
         <v>29.99</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="1" t="n">
         <v>-22.59</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="1" t="n">
         <v>2308</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="1" t="n">
         <v>3758.35</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>1</v>
       </c>
     </row>
